--- a/old/_261023_230000_Black Friday.xlsx
+++ b/old/_261023_230000_Black Friday.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48384C0F-1DD1-4E96-AFCC-5EE86136839F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA08D9A-96C0-4821-9CA3-B22410015B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8590" yWindow="3400" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11580" yWindow="3550" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,19 +210,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="6"/>
-      <color rgb="FF222222"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -245,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -267,8 +254,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -576,35 +561,35 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-    </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C13" s="15"/>
     </row>
@@ -617,20 +602,10 @@
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C16" s="15"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C17" s="15"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="C18" s="21"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C20" s="15"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C21" s="15"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C28" s="17"/>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
